--- a/artifacts/piston-rh/public/PistonRH_Import_Template.xlsx
+++ b/artifacts/piston-rh/public/PistonRH_Import_Template.xlsx
@@ -309,7 +309,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B44"/>
+  <dimension ref="A1:B46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="72" customWidth="1" min="1" max="1"/>
@@ -323,7 +323,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -331,7 +330,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
@@ -388,7 +386,6 @@
         </is>
       </c>
     </row>
-    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
@@ -403,7 +400,6 @@
         </is>
       </c>
     </row>
-    <row r="16"/>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
@@ -418,8 +414,6 @@
         </is>
       </c>
     </row>
-    <row r="19"/>
-    <row r="20"/>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
@@ -448,7 +442,6 @@
         </is>
       </c>
     </row>
-    <row r="25"/>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
@@ -470,7 +463,6 @@
         </is>
       </c>
     </row>
-    <row r="29"/>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
@@ -478,7 +470,6 @@
         </is>
       </c>
     </row>
-    <row r="31"/>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
@@ -539,7 +530,6 @@
         </is>
       </c>
     </row>
-    <row r="37"/>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
@@ -579,6 +569,20 @@
       <c r="A44" t="inlineStr">
         <is>
           <t xml:space="preserve">   overhauled. Leave blank if unknown. Format: YYYY-MM-DD (e.g. 2025-04-15).</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>-  Valve sheets also take 'Last Overhaul RH (hrs)': the component's own running hours at its</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   last overhaul. When set, overhaul-due status counts hours run since that overhaul.</t>
         </is>
       </c>
     </row>
@@ -1556,7 +1560,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J53"/>
+  <dimension ref="A1:K53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1568,6 +1572,7 @@
     <col width="12.44140625" customWidth="1" min="7" max="7"/>
     <col width="28" customWidth="1" min="8" max="8"/>
     <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="24" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="24.3" customHeight="1">
@@ -1625,6 +1630,12 @@
 (YYYY-MM-DD, optional)</t>
         </is>
       </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Last Overhaul RH (hrs)
+(component RH at overhaul, optional)</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="10.2" customHeight="1">
       <c r="A2" t="inlineStr">
@@ -1754,6 +1765,9 @@
           <t>2025-04-05</t>
         </is>
       </c>
+      <c r="K4" t="n">
+        <v>5000</v>
+      </c>
     </row>
     <row r="5" ht="10.2" customHeight="1">
       <c r="A5" t="inlineStr">
@@ -1797,6 +1811,9 @@
           <t>2025-04-06</t>
         </is>
       </c>
+      <c r="K5" t="n">
+        <v>5000</v>
+      </c>
     </row>
     <row r="6" ht="10.2" customHeight="1">
       <c r="A6" t="inlineStr">
@@ -1883,6 +1900,9 @@
           <t>2025-04-08</t>
         </is>
       </c>
+      <c r="K7" t="n">
+        <v>550</v>
+      </c>
     </row>
     <row r="8" ht="10.2" customHeight="1">
       <c r="A8" t="inlineStr">
@@ -1969,6 +1989,9 @@
           <t>2025-04-01</t>
         </is>
       </c>
+      <c r="K9" t="n">
+        <v>600</v>
+      </c>
     </row>
     <row r="10" ht="10.2" customHeight="1">
       <c r="A10" t="inlineStr">
@@ -2055,6 +2078,9 @@
           <t>2025-04-03</t>
         </is>
       </c>
+      <c r="K11" t="n">
+        <v>650</v>
+      </c>
     </row>
     <row r="12" ht="10.2" customHeight="1">
       <c r="A12" t="inlineStr">
@@ -2140,6 +2166,9 @@
         <is>
           <t>2025-04-05</t>
         </is>
+      </c>
+      <c r="K13" t="n">
+        <v>700</v>
       </c>
     </row>
     <row r="14" ht="10.2" customHeight="1">
@@ -3548,7 +3577,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J23"/>
+  <dimension ref="A1:K23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3560,6 +3589,7 @@
     <col width="12.44140625" customWidth="1" min="7" max="7"/>
     <col width="28" customWidth="1" min="8" max="8"/>
     <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="24" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="24.3" customHeight="1">
@@ -3617,6 +3647,12 @@
 (YYYY-MM-DD, optional)</t>
         </is>
       </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Last Overhaul RH (hrs)
+(component RH at overhaul, optional)</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="10.2" customHeight="1">
       <c r="A2" t="inlineStr">
@@ -3703,6 +3739,9 @@
           <t>2025-02-13</t>
         </is>
       </c>
+      <c r="K3" t="n">
+        <v>700</v>
+      </c>
     </row>
     <row r="4" ht="10.2" customHeight="1">
       <c r="A4" t="inlineStr">
@@ -3746,6 +3785,9 @@
           <t>2025-02-14</t>
         </is>
       </c>
+      <c r="K4" t="n">
+        <v>1050</v>
+      </c>
     </row>
     <row r="5" ht="10.2" customHeight="1">
       <c r="A5" t="inlineStr">
@@ -3789,6 +3831,9 @@
           <t>2025-02-15</t>
         </is>
       </c>
+      <c r="K5" t="n">
+        <v>1400</v>
+      </c>
     </row>
     <row r="6" ht="10.2" customHeight="1">
       <c r="A6" t="inlineStr">
@@ -3832,6 +3877,9 @@
           <t>2025-02-16</t>
         </is>
       </c>
+      <c r="K6" t="n">
+        <v>1750</v>
+      </c>
     </row>
     <row r="7" ht="10.2" customHeight="1">
       <c r="A7" t="inlineStr">
@@ -3874,6 +3922,9 @@
         <is>
           <t>2025-02-17</t>
         </is>
+      </c>
+      <c r="K7" t="n">
+        <v>2100</v>
       </c>
     </row>
     <row r="8" ht="10.2" customHeight="1">

--- a/artifacts/piston-rh/public/PistonRH_Import_Template.xlsx
+++ b/artifacts/piston-rh/public/PistonRH_Import_Template.xlsx
@@ -323,6 +323,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -330,6 +331,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
@@ -386,6 +388,7 @@
         </is>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
@@ -400,6 +403,7 @@
         </is>
       </c>
     </row>
+    <row r="16"/>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
@@ -414,6 +418,8 @@
         </is>
       </c>
     </row>
+    <row r="19"/>
+    <row r="20"/>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
@@ -442,6 +448,7 @@
         </is>
       </c>
     </row>
+    <row r="25"/>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
@@ -463,6 +470,7 @@
         </is>
       </c>
     </row>
+    <row r="29"/>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
@@ -470,6 +478,7 @@
         </is>
       </c>
     </row>
+    <row r="31"/>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
@@ -530,6 +539,7 @@
         </is>
       </c>
     </row>
+    <row r="37"/>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
@@ -537,6 +547,7 @@
         </is>
       </c>
     </row>
+    <row r="39"/>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
@@ -575,14 +586,14 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>-  Valve sheets also take 'Last Overhaul RH (hrs)': the component's own running hours at its</t>
+          <t>-  Valve sheets also take 'Last Overhaul RH (hrs)': the MAIN ENGINE total RH at which that</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t xml:space="preserve">   last overhaul. When set, overhaul-due status counts hours run since that overhaul.</t>
+          <t xml:space="preserve">   component was last overhauled. Overhaul-due status then counts ME hours run since that point.</t>
         </is>
       </c>
     </row>
@@ -683,6 +694,7 @@
         </is>
       </c>
     </row>
+    <row r="8"/>
     <row r="9" ht="13.95" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
@@ -724,6 +736,7 @@
         <v>20000</v>
       </c>
     </row>
+    <row r="13"/>
     <row r="14" ht="13.95" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
@@ -767,6 +780,7 @@
         </is>
       </c>
     </row>
+    <row r="18"/>
     <row r="19" ht="13.95" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
@@ -798,6 +812,7 @@
         </is>
       </c>
     </row>
+    <row r="22"/>
     <row r="23" ht="13.95" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
@@ -1633,7 +1648,7 @@
       <c r="K1" t="inlineStr">
         <is>
           <t>Last Overhaul RH (hrs)
-(component RH at overhaul, optional)</t>
+(ME RH at overhaul, optional)</t>
         </is>
       </c>
     </row>
@@ -1766,7 +1781,7 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>5000</v>
+        <v>14500</v>
       </c>
     </row>
     <row r="5" ht="10.2" customHeight="1">
@@ -1812,7 +1827,7 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>5000</v>
+        <v>13300</v>
       </c>
     </row>
     <row r="6" ht="10.2" customHeight="1">
@@ -1901,7 +1916,7 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>550</v>
+        <v>12100</v>
       </c>
     </row>
     <row r="8" ht="10.2" customHeight="1">
@@ -1990,7 +2005,7 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>600</v>
+        <v>10900</v>
       </c>
     </row>
     <row r="10" ht="10.2" customHeight="1">
@@ -2079,7 +2094,7 @@
         </is>
       </c>
       <c r="K11" t="n">
-        <v>650</v>
+        <v>9700</v>
       </c>
     </row>
     <row r="12" ht="10.2" customHeight="1">
@@ -2168,7 +2183,7 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>700</v>
+        <v>8500</v>
       </c>
     </row>
     <row r="14" ht="10.2" customHeight="1">
@@ -3650,7 +3665,7 @@
       <c r="K1" t="inlineStr">
         <is>
           <t>Last Overhaul RH (hrs)
-(component RH at overhaul, optional)</t>
+(ME RH at overhaul, optional)</t>
         </is>
       </c>
     </row>
@@ -3740,7 +3755,7 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>700</v>
+        <v>14500</v>
       </c>
     </row>
     <row r="4" ht="10.2" customHeight="1">
@@ -3786,7 +3801,7 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>1050</v>
+        <v>13300</v>
       </c>
     </row>
     <row r="5" ht="10.2" customHeight="1">
@@ -3832,7 +3847,7 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>1400</v>
+        <v>12100</v>
       </c>
     </row>
     <row r="6" ht="10.2" customHeight="1">
@@ -3878,7 +3893,7 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>1750</v>
+        <v>10900</v>
       </c>
     </row>
     <row r="7" ht="10.2" customHeight="1">
@@ -3924,7 +3939,7 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>2100</v>
+        <v>9700</v>
       </c>
     </row>
     <row r="8" ht="10.2" customHeight="1">
